--- a/Result/profitability/1734.xlsx
+++ b/Result/profitability/1734.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.405</v>
+        <v>0.43375</v>
       </c>
       <c r="N2" t="n">
-        <v>41.45124999999999</v>
+        <v>42.7725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39125</v>
+        <v>0.39625</v>
       </c>
       <c r="N3" t="n">
-        <v>41.8875</v>
+        <v>42.66</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3375</v>
+        <v>0.32125</v>
       </c>
       <c r="N4" t="n">
-        <v>41.4875</v>
+        <v>41.98625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.27375</v>
+        <v>0.2875</v>
       </c>
       <c r="N5" t="n">
-        <v>40.425</v>
+        <v>40.95625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26625</v>
+        <v>0.2725</v>
       </c>
       <c r="N6" t="n">
-        <v>40.095</v>
+        <v>40.47499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.25625</v>
+        <v>0.25</v>
       </c>
       <c r="N7" t="n">
-        <v>39.52625</v>
+        <v>39.9525</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.21875</v>
+        <v>0.23125</v>
       </c>
       <c r="N8" t="n">
-        <v>39.24375</v>
+        <v>39.62125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>871</v>
+      </c>
+      <c r="D75" t="n">
+        <v>463</v>
+      </c>
+      <c r="E75" t="n">
+        <v>408</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>112</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>107</v>
+      </c>
+      <c r="K75" t="n">
+        <v>93</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.5625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.019999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06887115165336355</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09971844204598779</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
